--- a/Ft-Cloud/ft-services/ft-service-sp/src/main/resources/template/importSgjsTechnicalFileBlueprint.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-sp/src/main/resources/template/importSgjsTechnicalFileBlueprint.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27628"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fushudong\workspace20230814\opmp\Ft-Cloud\ft-services\ft-service-sp\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C801D03-51B0-495E-B29C-1EE73D8E1300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BFB0C1F-D4D2-4F1D-AD44-ED4C49D5CF3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="2024-06-17" sheetId="1" r:id="rId1"/>
+    <sheet name="2023-07-05" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -23,9 +23,11 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>图纸编号</t>
-  </si>
-  <si>
-    <t>版本</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>图纸名称（必填）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>发放图纸数量</t>
@@ -34,39 +36,11 @@
     <t>计划开工日期</t>
   </si>
   <si>
+    <t>图纸发放人（必填）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>图纸发放日期</t>
-  </si>
-  <si>
-    <t>是否变更后图纸</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>图纸名称</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（必填）</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>图纸发放人（必填）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -91,19 +65,57 @@
       </rPr>
       <t>（必填）</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否变更后图纸</t>
+  </si>
+  <si>
+    <t>版本</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
-      <name val="等线"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="微软雅黑"/>
       <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -111,13 +123,7 @@
       <sz val="10"/>
       <color indexed="9"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -131,6 +137,14 @@
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -139,12 +153,12 @@
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="136"/>
+      <name val="MS Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -154,15 +168,34 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="23"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="23"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -186,17 +219,38 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -217,7 +271,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -233,7 +287,7 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
         <a:srgbClr val="ED7D31"/>
@@ -245,7 +299,7 @@
         <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
         <a:srgbClr val="70AD47"/>
@@ -259,12 +313,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -292,31 +346,14 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -344,23 +381,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -503,67 +523,88 @@
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:O6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="4" width="16.75" customWidth="1"/>
-    <col min="5" max="5" width="24.25" customWidth="1"/>
-    <col min="6" max="7" width="16.75" customWidth="1"/>
-    <col min="8" max="8" width="20.75" customWidth="1"/>
-    <col min="9" max="9" width="16.75" customWidth="1"/>
+    <col min="1" max="1" width="16.875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.375" customWidth="1"/>
+    <col min="3" max="3" width="16.5" customWidth="1"/>
+    <col min="4" max="4" width="19.25" customWidth="1"/>
+    <col min="5" max="5" width="20.5" customWidth="1"/>
+    <col min="6" max="6" width="28.125" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="36.75" customWidth="1"/>
+    <col min="9" max="9" width="17.625" customWidth="1"/>
+    <col min="10" max="10" width="11.625" customWidth="1"/>
+    <col min="11" max="11" width="12.625" customWidth="1"/>
+    <col min="13" max="13" width="12.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:15" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="2" t="s">
+      <c r="I1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>5</v>
-      </c>
+    </row>
+    <row r="2" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="L2" s="6"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A3" s="2"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A4" s="2"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A5" s="2"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A6" s="2"/>
+      <c r="O6" s="6"/>
     </row>
   </sheetData>
-  <dataConsolidate/>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="2">
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1 E2:E1048576" xr:uid="{7D10ED0F-93B6-47B4-A868-53DD8DC1D7A0}">
+  <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations count="3">
+    <dataValidation showInputMessage="1" showErrorMessage="1" sqref="B1:B1048576" xr:uid="{8C7B18EB-1706-4693-9E43-8A9FE2C13F13}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1:I1048576" xr:uid="{6D80C78C-AA37-4F06-B58A-97939651B82E}">
+      <formula1>"否,是"</formula1>
+    </dataValidation>
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1" xr:uid="{D10C0652-558B-4321-941B-F83B48D5BB24}">
       <formula1>1</formula1>
       <formula2>73051</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1:I1048576" xr:uid="{03D02593-3A65-4D61-AF0D-901EEB539831}">
-      <formula1>"否,是"</formula1>
-    </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Ft-Cloud/ft-services/ft-service-sp/src/main/resources/template/importSgjsTechnicalFileBlueprint.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-sp/src/main/resources/template/importSgjsTechnicalFileBlueprint.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fushudong\workspace20230814\opmp\Ft-Cloud\ft-services\ft-service-sp\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BFB0C1F-D4D2-4F1D-AD44-ED4C49D5CF3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{739E9E16-2EB9-4F54-B0DE-EE668358D7A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -537,7 +537,7 @@
     <col min="4" max="4" width="19.25" customWidth="1"/>
     <col min="5" max="5" width="20.5" customWidth="1"/>
     <col min="6" max="6" width="28.125" customWidth="1"/>
-    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="7" max="7" width="20.375" customWidth="1"/>
     <col min="8" max="8" width="36.75" customWidth="1"/>
     <col min="9" max="9" width="17.625" customWidth="1"/>
     <col min="10" max="10" width="11.625" customWidth="1"/>
@@ -577,6 +577,8 @@
     <row r="2" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="5"/>
       <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="G2" s="5"/>
       <c r="L2" s="6"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.15">
@@ -594,14 +596,26 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="3">
+  <dataValidations count="6">
     <dataValidation showInputMessage="1" showErrorMessage="1" sqref="B1:B1048576" xr:uid="{8C7B18EB-1706-4693-9E43-8A9FE2C13F13}"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1:I1048576" xr:uid="{6D80C78C-AA37-4F06-B58A-97939651B82E}">
       <formula1>"否,是"</formula1>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1" xr:uid="{D10C0652-558B-4321-941B-F83B48D5BB24}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="超出输入范围（0~9999）" sqref="D1:D3 D5:D1048576" xr:uid="{C4240003-2E9D-4DF6-A7EF-FABFA10FAB34}">
+      <formula1>0</formula1>
+      <formula2>9999</formula2>
+    </dataValidation>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="请输入0~9999整数" sqref="D4" xr:uid="{20ECF2DE-1459-4F9D-ACE1-86147432256A}">
+      <formula1>0</formula1>
+      <formula2>9999</formula2>
+    </dataValidation>
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="请输入日期格式，范围（1900年~2200年）" sqref="E1:E1048576" xr:uid="{F42E4F19-A743-4912-B88A-14A53E8D73E7}">
       <formula1>1</formula1>
       <formula2>73051</formula2>
+    </dataValidation>
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="请输入日期格式，范围（1900年~2200年）" sqref="G1:G1048576" xr:uid="{3C300071-A89C-4C0C-B748-310F0648C4ED}">
+      <formula1>32874</formula1>
+      <formula2>109575</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Ft-Cloud/ft-services/ft-service-sp/src/main/resources/template/importSgjsTechnicalFileBlueprint.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-sp/src/main/resources/template/importSgjsTechnicalFileBlueprint.xlsx
@@ -1,21 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fushudong\workspace20230814\opmp\Ft-Cloud\ft-services\ft-service-sp\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{739E9E16-2EB9-4F54-B0DE-EE668358D7A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84648199-9A6F-4F66-8843-AFBDE49EC1A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="2023-07-05" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -23,11 +28,15 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>图纸编号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>图纸名称（必填）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>版本</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>发放图纸数量</t>
@@ -37,7 +46,7 @@
   </si>
   <si>
     <t>图纸发放人（必填）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>图纸发放日期</t>
@@ -65,33 +74,25 @@
       </rPr>
       <t>（必填）</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>是否变更后图纸</t>
-  </si>
-  <si>
-    <t>版本</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
+  </numFmts>
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -103,20 +104,19 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
+      <sz val="9"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="MS Gothic"/>
       <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <charset val="128"/>
     </font>
     <font>
       <b/>
@@ -148,14 +148,6 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="MS Gothic"/>
-      <family val="3"/>
-      <charset val="128"/>
     </font>
   </fonts>
   <fills count="4">
@@ -177,7 +169,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -189,7 +181,9 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -198,61 +192,34 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="23"/>
-      </left>
-      <right style="thin">
-        <color indexed="23"/>
-      </right>
-      <top style="thin">
-        <color indexed="23"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="23"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -271,7 +238,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -313,12 +280,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="Yu Gothic Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -348,12 +315,12 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="Yu Gothic"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -523,102 +490,80 @@
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.375" customWidth="1"/>
-    <col min="3" max="3" width="16.5" customWidth="1"/>
-    <col min="4" max="4" width="19.25" customWidth="1"/>
-    <col min="5" max="5" width="20.5" customWidth="1"/>
-    <col min="6" max="6" width="28.125" customWidth="1"/>
-    <col min="7" max="7" width="20.375" customWidth="1"/>
-    <col min="8" max="8" width="36.75" customWidth="1"/>
-    <col min="9" max="9" width="17.625" customWidth="1"/>
-    <col min="10" max="10" width="11.625" customWidth="1"/>
-    <col min="11" max="11" width="12.625" customWidth="1"/>
-    <col min="13" max="13" width="12.125" customWidth="1"/>
+    <col min="1" max="1" width="17.109375" customWidth="1"/>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="14.44140625" customWidth="1"/>
+    <col min="4" max="4" width="21" customWidth="1"/>
+    <col min="5" max="5" width="22.33203125" style="8" customWidth="1"/>
+    <col min="6" max="6" width="19.21875" customWidth="1"/>
+    <col min="7" max="7" width="23.88671875" style="8" customWidth="1"/>
+    <col min="8" max="8" width="24.21875" customWidth="1"/>
+    <col min="9" max="9" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:9" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>7</v>
-      </c>
     </row>
-    <row r="2" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="L2" s="6"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A3" s="2"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A4" s="2"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A5" s="2"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A6" s="2"/>
-      <c r="O6" s="6"/>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G2" s="8">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="6">
-    <dataValidation showInputMessage="1" showErrorMessage="1" sqref="B1:B1048576" xr:uid="{8C7B18EB-1706-4693-9E43-8A9FE2C13F13}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1:I1048576" xr:uid="{6D80C78C-AA37-4F06-B58A-97939651B82E}">
+  <phoneticPr fontId="2" type="noConversion"/>
+  <dataValidations count="4">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="请输入日期格式，例如：2022年1月1日，输入范围（1900年~2200年）" sqref="E1:E1048576 G1:G1048576" xr:uid="{783735FA-EB5C-4E19-899B-E7770E1ACD4B}">
+      <formula1>1</formula1>
+      <formula2>109575</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1:I1048576" xr:uid="{B5073AA6-3A0C-46E7-BBB7-A810CA493B70}">
       <formula1>"否,是"</formula1>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="超出输入范围（0~9999）" sqref="D1:D3 D5:D1048576" xr:uid="{C4240003-2E9D-4DF6-A7EF-FABFA10FAB34}">
+    <dataValidation showInputMessage="1" showErrorMessage="1" sqref="B1" xr:uid="{CA61280F-8B84-4A09-95EE-77435792284A}"/>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="超出输入范围（0~9999）" sqref="D1:D1048576" xr:uid="{DD9CE6FC-0A30-416A-A222-FAE23047BBEC}">
       <formula1>0</formula1>
       <formula2>9999</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="请输入0~9999整数" sqref="D4" xr:uid="{20ECF2DE-1459-4F9D-ACE1-86147432256A}">
-      <formula1>0</formula1>
-      <formula2>9999</formula2>
-    </dataValidation>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="请输入日期格式，范围（1900年~2200年）" sqref="E1:E1048576" xr:uid="{F42E4F19-A743-4912-B88A-14A53E8D73E7}">
-      <formula1>1</formula1>
-      <formula2>73051</formula2>
-    </dataValidation>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="请输入日期格式，范围（1900年~2200年）" sqref="G1:G1048576" xr:uid="{3C300071-A89C-4C0C-B748-310F0648C4ED}">
-      <formula1>32874</formula1>
-      <formula2>109575</formula2>
-    </dataValidation>
   </dataValidations>
-  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Ft-Cloud/ft-services/ft-service-sp/src/main/resources/template/importSgjsTechnicalFileBlueprint.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-sp/src/main/resources/template/importSgjsTechnicalFileBlueprint.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fushudong\workspace20230814\opmp\Ft-Cloud\ft-services\ft-service-sp\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84648199-9A6F-4F66-8843-AFBDE49EC1A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB6CD9B-BD88-4830-B341-F8D3F9FCA376}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>图纸编号</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -52,32 +52,15 @@
     <t>图纸发放日期</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>图纸接收人</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（必填）</t>
-    </r>
+    <t>是否变更后图纸</t>
+  </si>
+  <si>
+    <t>图纸接收人（必填）</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>是否变更后图纸</t>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -87,7 +70,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -113,40 +96,17 @@
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="MS Gothic"/>
-      <family val="3"/>
-      <charset val="128"/>
+      <color indexed="9"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <color indexed="9"/>
-      <name val="Arial"/>
+      <color rgb="FF990033"/>
+      <name val="微软雅黑"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Microsoft JhengHei"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -179,16 +139,16 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -196,27 +156,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -226,6 +180,12 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF990033"/>
+      <color rgb="FFCC0000"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -503,65 +463,65 @@
   <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.109375" customWidth="1"/>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="14.44140625" customWidth="1"/>
-    <col min="4" max="4" width="21" customWidth="1"/>
-    <col min="5" max="5" width="22.33203125" style="8" customWidth="1"/>
-    <col min="6" max="6" width="19.21875" customWidth="1"/>
-    <col min="7" max="7" width="23.88671875" style="8" customWidth="1"/>
-    <col min="8" max="8" width="24.21875" customWidth="1"/>
-    <col min="9" max="9" width="23" customWidth="1"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="19.21875" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" customWidth="1"/>
+    <col min="4" max="4" width="23.21875" customWidth="1"/>
+    <col min="5" max="5" width="25.77734375" style="6" customWidth="1"/>
+    <col min="6" max="6" width="24.5546875" customWidth="1"/>
+    <col min="7" max="7" width="21.6640625" style="6" customWidth="1"/>
+    <col min="8" max="8" width="23.109375" customWidth="1"/>
+    <col min="9" max="9" width="23.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>7</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G2" s="8">
-        <v>1</v>
+      <c r="B2" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="请输入日期格式，例如：2022年1月1日，输入范围（1900年~2200年）" sqref="E1:E1048576 G1:G1048576" xr:uid="{783735FA-EB5C-4E19-899B-E7770E1ACD4B}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="请输入整数，输入范围（0~9999）" sqref="D1:D1048576" xr:uid="{1F0CBC20-004D-4CC8-8618-A91A49F436C6}">
+      <formula1>0</formula1>
+      <formula2>9999</formula2>
+    </dataValidation>
+    <dataValidation showInputMessage="1" showErrorMessage="1" sqref="B1" xr:uid="{277DA7F7-35E8-41EF-9678-9B5E92F5ABFF}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1:I1048576" xr:uid="{9CFF83DB-D6D1-4000-8865-7FD105ED74F4}">
+      <formula1>"否,是"</formula1>
+    </dataValidation>
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="请输入日期格式，例如：2022年1月1日，输入范围（1900年~2200年）" sqref="G1:G1048576 E1:E1048576" xr:uid="{B9F26903-F3AF-4782-8141-998651025BE6}">
       <formula1>1</formula1>
       <formula2>109575</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1:I1048576" xr:uid="{B5073AA6-3A0C-46E7-BBB7-A810CA493B70}">
-      <formula1>"否,是"</formula1>
-    </dataValidation>
-    <dataValidation showInputMessage="1" showErrorMessage="1" sqref="B1" xr:uid="{CA61280F-8B84-4A09-95EE-77435792284A}"/>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="超出输入范围（0~9999）" sqref="D1:D1048576" xr:uid="{DD9CE6FC-0A30-416A-A222-FAE23047BBEC}">
-      <formula1>0</formula1>
-      <formula2>9999</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Ft-Cloud/ft-services/ft-service-sp/src/main/resources/template/importSgjsTechnicalFileBlueprint.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-sp/src/main/resources/template/importSgjsTechnicalFileBlueprint.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fushudong\workspace20230814\opmp\Ft-Cloud\ft-services\ft-service-sp\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB6CD9B-BD88-4830-B341-F8D3F9FCA376}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09911089-1442-41DF-8C1E-98243C0BBFA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4044" yWindow="4044" windowWidth="23040" windowHeight="12264" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,11 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t>图纸编号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>图纸名称（必填）</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -60,6 +56,14 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>层级编码（必填）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>图纸编号（必填）</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -156,11 +160,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -174,6 +175,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -460,69 +465,74 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="19.21875" customWidth="1"/>
-    <col min="3" max="3" width="13.109375" customWidth="1"/>
-    <col min="4" max="4" width="23.21875" customWidth="1"/>
-    <col min="5" max="5" width="25.77734375" style="6" customWidth="1"/>
-    <col min="6" max="6" width="24.5546875" customWidth="1"/>
-    <col min="7" max="7" width="21.6640625" style="6" customWidth="1"/>
-    <col min="8" max="8" width="23.109375" customWidth="1"/>
-    <col min="9" max="9" width="23.5546875" customWidth="1"/>
+    <col min="1" max="1" width="19.88671875" style="7" customWidth="1"/>
+    <col min="2" max="2" width="22.77734375" customWidth="1"/>
+    <col min="3" max="3" width="19.21875" customWidth="1"/>
+    <col min="4" max="4" width="13.109375" customWidth="1"/>
+    <col min="5" max="5" width="23.21875" customWidth="1"/>
+    <col min="6" max="6" width="25.77734375" style="5" customWidth="1"/>
+    <col min="7" max="7" width="24.5546875" customWidth="1"/>
+    <col min="8" max="8" width="21.6640625" style="5" customWidth="1"/>
+    <col min="9" max="9" width="23.109375" customWidth="1"/>
+    <col min="10" max="10" width="23.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="H1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="I1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
         <v>8</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="4">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="请输入整数，输入范围（0~9999）" sqref="D1:D1048576" xr:uid="{1F0CBC20-004D-4CC8-8618-A91A49F436C6}">
+  <dataValidations count="5">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="请输入整数，输入范围（0~9999）" sqref="E1:E1048576" xr:uid="{1F0CBC20-004D-4CC8-8618-A91A49F436C6}">
       <formula1>0</formula1>
       <formula2>9999</formula2>
     </dataValidation>
-    <dataValidation showInputMessage="1" showErrorMessage="1" sqref="B1" xr:uid="{277DA7F7-35E8-41EF-9678-9B5E92F5ABFF}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1:I1048576" xr:uid="{9CFF83DB-D6D1-4000-8865-7FD105ED74F4}">
+    <dataValidation showInputMessage="1" showErrorMessage="1" sqref="C1" xr:uid="{277DA7F7-35E8-41EF-9678-9B5E92F5ABFF}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J1:J1048576" xr:uid="{9CFF83DB-D6D1-4000-8865-7FD105ED74F4}">
       <formula1>"否,是"</formula1>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="请输入日期格式，例如：2022年1月1日，输入范围（1900年~2200年）" sqref="G1:G1048576 E1:E1048576" xr:uid="{B9F26903-F3AF-4782-8141-998651025BE6}">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="请输入日期格式，例如：2022年1月1日，输入范围（1900年~2200年）" sqref="H1:H1048576 F1:F1048576" xr:uid="{B9F26903-F3AF-4782-8141-998651025BE6}">
       <formula1>1</formula1>
       <formula2>109575</formula2>
     </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="请按照以下格式输入：_x000a_1_x000a_1-1_x000a_1-2_x000a_2_x000a_2-1" sqref="A1:A1048576" xr:uid="{561BAB63-4ADE-4067-9194-735CE4F4C3C2}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Ft-Cloud/ft-services/ft-service-sp/src/main/resources/template/importSgjsTechnicalFileBlueprint.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-sp/src/main/resources/template/importSgjsTechnicalFileBlueprint.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fushudong\workspace20230814\opmp\Ft-Cloud\ft-services\ft-service-sp\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09911089-1442-41DF-8C1E-98243C0BBFA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71898495-1DAC-4C3B-8289-932DECB5180B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4044" yWindow="4044" windowWidth="23040" windowHeight="12264" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,10 +27,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
-    <t>图纸名称（必填）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>版本</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -41,20 +37,12 @@
     <t>计划开工日期</t>
   </si>
   <si>
-    <t>图纸发放人（必填）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>图纸发放日期</t>
   </si>
   <si>
     <t>是否变更后图纸</t>
   </si>
   <si>
-    <t>图纸接收人（必填）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -64,6 +52,18 @@
   </si>
   <si>
     <t>图纸编号（必填）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>图纸名称</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>图纸发放人</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>图纸接收人</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -482,39 +482,39 @@
   <sheetData>
     <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="H1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="4" t="s">
+      <c r="J1" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
